--- a/03_Outputs/Vulnerable_ref_dept/04_Cluster/Summary_Stats.xlsx
+++ b/03_Outputs/Vulnerable_ref_dept/04_Cluster/Summary_Stats.xlsx
@@ -406,7 +406,7 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>-0.07954633101253777</v>
+        <v>-0.0795463310125378</v>
       </c>
       <c r="E2">
         <v>1.753007854822983</v>
@@ -415,7 +415,7 @@
         <v>-8.736590198195003</v>
       </c>
       <c r="G2">
-        <v>0.570076350306586</v>
+        <v>0.5700763503065862</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>0.6233449243940841</v>
+        <v>0.6233449243940837</v>
       </c>
       <c r="E3">
         <v>1.263711219263236</v>
       </c>
       <c r="F3">
-        <v>-1.27039567499963</v>
+        <v>-1.270395674999631</v>
       </c>
       <c r="G3">
         <v>3.27492217455772</v>
@@ -460,16 +460,16 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>0.1762155225130505</v>
+        <v>0.1762155225130516</v>
       </c>
       <c r="E4">
-        <v>0.9611864598041754</v>
+        <v>0.9611864598041751</v>
       </c>
       <c r="F4">
-        <v>-1.558949274954841</v>
+        <v>-1.558949274954837</v>
       </c>
       <c r="G4">
-        <v>2.338950246282719</v>
+        <v>2.338950246282722</v>
       </c>
     </row>
     <row r="5">
@@ -487,7 +487,7 @@
         <v>27</v>
       </c>
       <c r="D5">
-        <v>0.6891274661563618</v>
+        <v>0.6891274661563617</v>
       </c>
       <c r="E5">
         <v>1.336378995937455</v>
@@ -496,7 +496,7 @@
         <v>-2.676226615379075</v>
       </c>
       <c r="G5">
-        <v>2.989090349946455</v>
+        <v>2.989090349946458</v>
       </c>
     </row>
     <row r="6">
@@ -514,16 +514,16 @@
         <v>27</v>
       </c>
       <c r="D6">
-        <v>0.139834181717716</v>
+        <v>0.1398341817177167</v>
       </c>
       <c r="E6">
         <v>1.110277606390108</v>
       </c>
       <c r="F6">
-        <v>-2.313289150362545</v>
+        <v>-2.313289150362547</v>
       </c>
       <c r="G6">
-        <v>2.254622989650819</v>
+        <v>2.254622989650821</v>
       </c>
     </row>
     <row r="7">
@@ -541,16 +541,16 @@
         <v>27</v>
       </c>
       <c r="D7">
-        <v>-0.9003829705041834</v>
+        <v>-0.9003829705041816</v>
       </c>
       <c r="E7">
         <v>1.154648255571175</v>
       </c>
       <c r="F7">
-        <v>-3.249702474870532</v>
+        <v>-3.249702474870527</v>
       </c>
       <c r="G7">
-        <v>0.8481406982936234</v>
+        <v>0.8481406982936298</v>
       </c>
     </row>
     <row r="8">
@@ -568,16 +568,16 @@
         <v>27</v>
       </c>
       <c r="D8">
-        <v>-0.3513340987110236</v>
+        <v>-0.3513340987110238</v>
       </c>
       <c r="E8">
         <v>0.6452554795040338</v>
       </c>
       <c r="F8">
-        <v>-1.682869142169337</v>
+        <v>-1.682869142169336</v>
       </c>
       <c r="G8">
-        <v>0.6390306423399892</v>
+        <v>0.6390306423399882</v>
       </c>
     </row>
     <row r="9">
@@ -595,16 +595,16 @@
         <v>27</v>
       </c>
       <c r="D9">
-        <v>0.007513057887142102</v>
+        <v>0.007513057887142238</v>
       </c>
       <c r="E9">
-        <v>0.2741732316716115</v>
+        <v>0.2741732316716113</v>
       </c>
       <c r="F9">
-        <v>-0.8126389195866297</v>
+        <v>-0.8126389195866289</v>
       </c>
       <c r="G9">
-        <v>0.5349101500053428</v>
+        <v>0.5349101500053425</v>
       </c>
     </row>
     <row r="10">
@@ -622,16 +622,16 @@
         <v>27</v>
       </c>
       <c r="D10">
-        <v>-1.245685134331066</v>
+        <v>-1.245685134331065</v>
       </c>
       <c r="E10">
         <v>1.225472388633442</v>
       </c>
       <c r="F10">
-        <v>-4.216579492924283</v>
+        <v>-4.216579492924284</v>
       </c>
       <c r="G10">
-        <v>0.5487719790679686</v>
+        <v>0.5487719790679692</v>
       </c>
     </row>
     <row r="11">
@@ -649,16 +649,16 @@
         <v>27</v>
       </c>
       <c r="D11">
-        <v>0.113111525696554</v>
+        <v>0.1131115256965526</v>
       </c>
       <c r="E11">
-        <v>1.413261091444586</v>
+        <v>1.413261091444585</v>
       </c>
       <c r="F11">
-        <v>-2.687799830217598</v>
+        <v>-2.687799830217599</v>
       </c>
       <c r="G11">
-        <v>3.149438304257336</v>
+        <v>3.149438304257332</v>
       </c>
     </row>
     <row r="12">
@@ -679,13 +679,13 @@
         <v>-0.888939510132157</v>
       </c>
       <c r="E12">
-        <v>0.4508474130969302</v>
+        <v>0.4508474130969299</v>
       </c>
       <c r="F12">
-        <v>-1.956045892917402</v>
+        <v>-1.956045892917401</v>
       </c>
       <c r="G12">
-        <v>-0.04983580321507906</v>
+        <v>-0.04983580321507982</v>
       </c>
     </row>
     <row r="13">
@@ -706,13 +706,13 @@
         <v>0.1400536856134299</v>
       </c>
       <c r="E13">
-        <v>0.7353710846101719</v>
+        <v>0.7353710846101721</v>
       </c>
       <c r="F13">
-        <v>-1.141688361501572</v>
+        <v>-1.141688361501571</v>
       </c>
       <c r="G13">
-        <v>1.819531707821401</v>
+        <v>1.819531707821403</v>
       </c>
     </row>
     <row r="14">
@@ -730,16 +730,16 @@
         <v>27</v>
       </c>
       <c r="D14">
-        <v>-0.2363741182354272</v>
+        <v>-0.236374118235427</v>
       </c>
       <c r="E14">
         <v>0.5583747249448445</v>
       </c>
       <c r="F14">
-        <v>-1.391054389289007</v>
+        <v>-1.391054389289006</v>
       </c>
       <c r="G14">
-        <v>0.6010657297068582</v>
+        <v>0.6010657297068608</v>
       </c>
     </row>
     <row r="15">
@@ -760,7 +760,7 @@
         <v>0.4162785387904007</v>
       </c>
       <c r="E15">
-        <v>0.9476612625538883</v>
+        <v>0.9476612625538882</v>
       </c>
       <c r="F15">
         <v>-1.006417913033536</v>
@@ -811,16 +811,16 @@
         <v>27</v>
       </c>
       <c r="D17">
-        <v>0.7947342643974874</v>
+        <v>0.794734264397487</v>
       </c>
       <c r="E17">
-        <v>1.39160805669952</v>
+        <v>1.391608056699519</v>
       </c>
       <c r="F17">
-        <v>-0.7601493886723355</v>
+        <v>-0.7601493886723358</v>
       </c>
       <c r="G17">
-        <v>4.665311989065716</v>
+        <v>4.665311989065708</v>
       </c>
     </row>
     <row r="18">
@@ -838,16 +838,16 @@
         <v>27</v>
       </c>
       <c r="D18">
-        <v>0.1920950679097997</v>
+        <v>0.1920950679098003</v>
       </c>
       <c r="E18">
-        <v>0.9394466062464207</v>
+        <v>0.9394466062464217</v>
       </c>
       <c r="F18">
         <v>-1.434712610124998</v>
       </c>
       <c r="G18">
-        <v>2.641314803312763</v>
+        <v>2.64131480331277</v>
       </c>
     </row>
     <row r="19">
@@ -865,16 +865,16 @@
         <v>27</v>
       </c>
       <c r="D19">
-        <v>0.1415329795785035</v>
+        <v>0.1415329795785038</v>
       </c>
       <c r="E19">
-        <v>0.8083375701890262</v>
+        <v>0.808337570189027</v>
       </c>
       <c r="F19">
-        <v>-1.705764145061318</v>
+        <v>-1.705764145061316</v>
       </c>
       <c r="G19">
-        <v>2.506776490831638</v>
+        <v>2.506776490831643</v>
       </c>
     </row>
     <row r="20">
@@ -892,16 +892,16 @@
         <v>27</v>
       </c>
       <c r="D20">
-        <v>-0.1455361435979811</v>
+        <v>-0.1455361435979803</v>
       </c>
       <c r="E20">
-        <v>0.7841117972527055</v>
+        <v>0.7841117972527051</v>
       </c>
       <c r="F20">
-        <v>-2.297341861876017</v>
+        <v>-2.297341861876018</v>
       </c>
       <c r="G20">
-        <v>1.127529337528537</v>
+        <v>1.127529337528539</v>
       </c>
     </row>
     <row r="21">
@@ -922,13 +922,13 @@
         <v>-1.035584309020858</v>
       </c>
       <c r="E21">
-        <v>0.8689381543664672</v>
+        <v>0.8689381543664676</v>
       </c>
       <c r="F21">
-        <v>-3.812198855986544</v>
+        <v>-3.812198855986547</v>
       </c>
       <c r="G21">
-        <v>0.6578095723342425</v>
+        <v>0.6578095723342421</v>
       </c>
     </row>
     <row r="22">
@@ -946,16 +946,16 @@
         <v>27</v>
       </c>
       <c r="D22">
-        <v>-0.779129661319247</v>
+        <v>-0.7791296613192467</v>
       </c>
       <c r="E22">
         <v>1.134977226277925</v>
       </c>
       <c r="F22">
-        <v>-4.054776522940765</v>
+        <v>-4.054776522940762</v>
       </c>
       <c r="G22">
-        <v>1.01815278955183</v>
+        <v>1.018152789551833</v>
       </c>
     </row>
     <row r="23">
@@ -973,7 +973,7 @@
         <v>27</v>
       </c>
       <c r="D23">
-        <v>-0.3495743922338137</v>
+        <v>-0.3495743922338128</v>
       </c>
       <c r="E23">
         <v>1.085984521927859</v>
@@ -982,7 +982,7 @@
         <v>-2.358897378628837</v>
       </c>
       <c r="G23">
-        <v>2.432821634141699</v>
+        <v>2.432821634141705</v>
       </c>
     </row>
     <row r="24">
@@ -1000,16 +1000,16 @@
         <v>27</v>
       </c>
       <c r="D24">
-        <v>0.3038616843278064</v>
+        <v>0.3038616843278023</v>
       </c>
       <c r="E24">
-        <v>1.211811743040827</v>
+        <v>1.211811743040814</v>
       </c>
       <c r="F24">
-        <v>-2.60225589667948</v>
+        <v>-2.602255896679408</v>
       </c>
       <c r="G24">
-        <v>2.810856373638918</v>
+        <v>2.810856373638819</v>
       </c>
     </row>
     <row r="25">
@@ -1030,13 +1030,13 @@
         <v>-1.246030805602292</v>
       </c>
       <c r="E25">
-        <v>0.9902188714129611</v>
+        <v>0.9902188714129609</v>
       </c>
       <c r="F25">
-        <v>-2.961308580693609</v>
+        <v>-2.961308580693608</v>
       </c>
       <c r="G25">
-        <v>0.7977511711634842</v>
+        <v>0.797751171163484</v>
       </c>
     </row>
     <row r="26">
@@ -1054,16 +1054,16 @@
         <v>27</v>
       </c>
       <c r="D26">
-        <v>-0.3099812914377787</v>
+        <v>-0.3099812914377795</v>
       </c>
       <c r="E26">
-        <v>0.9542139123250125</v>
+        <v>0.9542139123250123</v>
       </c>
       <c r="F26">
-        <v>-1.778262834253356</v>
+        <v>-1.778262834253358</v>
       </c>
       <c r="G26">
-        <v>1.412681618686449</v>
+        <v>1.412681618686447</v>
       </c>
     </row>
     <row r="27">
@@ -1087,10 +1087,10 @@
         <v>1.339268298751316</v>
       </c>
       <c r="F27">
-        <v>-5.536870042191997</v>
+        <v>-5.536870042191994</v>
       </c>
       <c r="G27">
-        <v>0.3498029729220694</v>
+        <v>0.3498029729220705</v>
       </c>
     </row>
     <row r="28">
@@ -1108,7 +1108,7 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>-0.1717600444845057</v>
+        <v>-0.1717600444845054</v>
       </c>
       <c r="E28">
         <v>1.544684590195141</v>
@@ -1117,7 +1117,7 @@
         <v>-3.895667876609284</v>
       </c>
       <c r="G28">
-        <v>2.951124406040775</v>
+        <v>2.951124406040776</v>
       </c>
     </row>
     <row r="29">
@@ -1144,7 +1144,7 @@
         <v>-1.898345467200467</v>
       </c>
       <c r="G29">
-        <v>0.9708529166678719</v>
+        <v>0.970852916667872</v>
       </c>
     </row>
     <row r="30">
@@ -1162,10 +1162,10 @@
         <v>27</v>
       </c>
       <c r="D30">
-        <v>0.1312309890816271</v>
+        <v>0.1312309890816272</v>
       </c>
       <c r="E30">
-        <v>0.7918608749055706</v>
+        <v>0.7918608749055704</v>
       </c>
       <c r="F30">
         <v>-1.827788362571081</v>
@@ -1189,13 +1189,13 @@
         <v>27</v>
       </c>
       <c r="D31">
-        <v>-0.784157543063449</v>
+        <v>-0.7841575430634488</v>
       </c>
       <c r="E31">
         <v>1.306585987215328</v>
       </c>
       <c r="F31">
-        <v>-3.955385643442785</v>
+        <v>-3.955385643442784</v>
       </c>
       <c r="G31">
         <v>1.062459622746978</v>
@@ -1216,16 +1216,16 @@
         <v>27</v>
       </c>
       <c r="D32">
-        <v>-0.1281170777522499</v>
+        <v>-0.1281170777522491</v>
       </c>
       <c r="E32">
-        <v>0.8816829815845126</v>
+        <v>0.8816829815845131</v>
       </c>
       <c r="F32">
-        <v>-1.30697796836533</v>
+        <v>-1.306977968365329</v>
       </c>
       <c r="G32">
-        <v>1.608035448913396</v>
+        <v>1.608035448913398</v>
       </c>
     </row>
     <row r="33">
@@ -1243,16 +1243,16 @@
         <v>27</v>
       </c>
       <c r="D33">
-        <v>-1.344539972542211</v>
+        <v>-1.333306474678199</v>
       </c>
       <c r="E33">
-        <v>0.6384846960967885</v>
+        <v>0.6331861456144395</v>
       </c>
       <c r="F33">
-        <v>-2.522157065559848</v>
+        <v>-2.716952867028563</v>
       </c>
       <c r="G33">
-        <v>0.5357538263751828</v>
+        <v>0.4169320794810083</v>
       </c>
     </row>
   </sheetData>
